--- a/Excel/Excel_Further_Functions.xlsx
+++ b/Excel/Excel_Further_Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uqdmiles\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uq-my.sharepoint.com/personal/uqdmiles_uq_edu_au/Documents/Desktop/Manual updates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DE7EF4-3C31-4C89-8F8B-94FE6E461930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{33DE7EF4-3C31-4C89-8F8B-94FE6E461930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EF8B4F1-2BD5-4C4C-942C-192838E1C672}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="886" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="886" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exams" sheetId="19" r:id="rId1"/>
@@ -1559,7 +1559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S68"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -1579,7 +1579,7 @@
     <col min="19" max="19" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -1645,7 +1645,10 @@
         <f>IF(H2&gt;85,7,IF(H2&gt;75,6,IF(H2&gt;65,5,IF(H2&gt;55,4,IF(H2&gt;50,3,IF(H2&gt;40,2,1))))))</f>
         <v>7</v>
       </c>
-      <c r="M2" s="16"/>
+      <c r="M2" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="N2" s="22"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20">
@@ -1673,7 +1676,10 @@
         <f t="shared" ref="I3:I62" si="0">IF(H3&gt;85,7,IF(H3&gt;75,6,IF(H3&gt;65,5,IF(H3&gt;55,4,IF(H3&gt;50,3,IF(H3&gt;40,2,1))))))</f>
         <v>7</v>
       </c>
-      <c r="M3" s="16"/>
+      <c r="M3" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="N3" s="24"/>
       <c r="P3" s="17"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
@@ -1709,7 +1715,10 @@
         <v>4</v>
       </c>
       <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
+      <c r="M4" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="N4" s="26"/>
       <c r="P4" s="17"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
@@ -3568,25 +3577,6 @@
       </c>
       <c r="L62" s="16"/>
       <c r="M62" s="16"/>
-    </row>
-    <row r="65" spans="13:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="66" spans="13:14" x14ac:dyDescent="0.25">
-      <c r="M66" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="N66" s="22"/>
-    </row>
-    <row r="67" spans="13:14" x14ac:dyDescent="0.25">
-      <c r="M67" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="N67" s="24"/>
-    </row>
-    <row r="68" spans="13:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M68" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="N68" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3681,266 +3671,270 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>126</v>
+        <v>284</v>
       </c>
       <c r="D2" s="9">
-        <v>29443</v>
+        <v>35981</v>
       </c>
       <c r="E2" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D2)/365.25,0)</f>
-        <v>44</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="F2" s="10"/>
       <c r="G2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L2" s="11">
-        <v>1276</v>
+        <v>1257</v>
       </c>
       <c r="M2" s="11">
-        <v>13202</v>
+        <v>5570</v>
       </c>
       <c r="N2" s="11">
-        <v>3858</v>
+        <v>5070</v>
       </c>
       <c r="O2" s="11">
-        <v>14009</v>
+        <v>8444</v>
       </c>
       <c r="P2" s="11">
-        <v>8824</v>
+        <v>10627</v>
       </c>
       <c r="Q2" s="11">
-        <v>5508</v>
+        <v>10242</v>
       </c>
       <c r="R2" s="11">
-        <v>3519</v>
+        <v>13650</v>
       </c>
       <c r="S2" s="11">
-        <v>14895</v>
+        <v>14082</v>
       </c>
       <c r="T2" s="12">
         <f>SUM(L2:S2)</f>
-        <v>65091</v>
+        <v>68942</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>137</v>
+        <v>279</v>
       </c>
       <c r="D3" s="9">
-        <v>32000</v>
+        <v>38047</v>
       </c>
       <c r="E3" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D3)/365.25,0)</f>
-        <v>37</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F3" s="10"/>
       <c r="G3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L3" s="11">
-        <v>13010</v>
+        <v>14767</v>
       </c>
       <c r="M3" s="11">
-        <v>8535</v>
+        <v>8994</v>
       </c>
       <c r="N3" s="11">
-        <v>5678</v>
+        <v>3061</v>
       </c>
       <c r="O3" s="11">
-        <v>13717</v>
+        <v>10262</v>
       </c>
       <c r="P3" s="11">
-        <v>2821</v>
+        <v>10822</v>
       </c>
       <c r="Q3" s="11">
-        <v>4343</v>
+        <v>1678</v>
       </c>
       <c r="R3" s="11">
-        <v>1832</v>
+        <v>8196</v>
       </c>
       <c r="S3" s="11">
-        <v>7942</v>
+        <v>13935</v>
       </c>
       <c r="T3" s="12">
         <f>SUM(L3:S3)</f>
-        <v>57878</v>
+        <v>71715</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>114</v>
+        <v>280</v>
       </c>
       <c r="D4" s="9">
-        <v>32527</v>
+        <v>33744</v>
       </c>
       <c r="E4" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D4)/365.25,0)</f>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F4" s="10"/>
       <c r="G4" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L4" s="11">
-        <v>5984</v>
+        <v>5474</v>
       </c>
       <c r="M4" s="11">
-        <v>14769</v>
+        <v>7328</v>
       </c>
       <c r="N4" s="11">
-        <v>10766</v>
+        <v>14340</v>
       </c>
       <c r="O4" s="11">
-        <v>9915</v>
+        <v>10558</v>
       </c>
       <c r="P4" s="11">
-        <v>12892</v>
+        <v>2042</v>
       </c>
       <c r="Q4" s="11">
-        <v>1840</v>
+        <v>7549</v>
       </c>
       <c r="R4" s="11">
-        <v>4402</v>
+        <v>13160</v>
       </c>
       <c r="S4" s="11">
-        <v>3825</v>
+        <v>13981</v>
       </c>
       <c r="T4" s="12">
         <f>SUM(L4:S4)</f>
-        <v>64393</v>
+        <v>74432</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="D5" s="9">
-        <v>33014</v>
+        <v>35488</v>
       </c>
       <c r="E5" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D5)/365.25,0)</f>
-        <v>35</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="F5" s="10"/>
       <c r="G5" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="5">
         <v>3</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>219</v>
+        <v>11</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L5" s="11">
-        <v>7735</v>
+        <v>4714</v>
       </c>
       <c r="M5" s="11">
-        <v>3896</v>
+        <v>7955</v>
       </c>
       <c r="N5" s="11">
-        <v>7631</v>
+        <v>1956</v>
       </c>
       <c r="O5" s="11">
-        <v>2919</v>
+        <v>12954</v>
       </c>
       <c r="P5" s="11">
-        <v>3155</v>
+        <v>3266</v>
       </c>
       <c r="Q5" s="11">
-        <v>10681</v>
+        <v>6088</v>
       </c>
       <c r="R5" s="11">
-        <v>7483</v>
+        <v>12951</v>
       </c>
       <c r="S5" s="11">
-        <v>2514</v>
+        <v>12579</v>
       </c>
       <c r="T5" s="12">
         <f>SUM(L5:S5)</f>
-        <v>46014</v>
+        <v>62463</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="D6" s="9">
-        <v>33703</v>
+        <v>36055</v>
       </c>
       <c r="E6" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D6)/365.25,0)</f>
-        <v>33</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F6" s="10"/>
       <c r="G6" s="5" t="s">
         <v>2</v>
       </c>
@@ -3948,7 +3942,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>11</v>
@@ -3957,420 +3951,422 @@
         <v>15</v>
       </c>
       <c r="L6" s="11">
-        <v>1200</v>
+        <v>5152</v>
       </c>
       <c r="M6" s="11">
-        <v>13819</v>
+        <v>1582</v>
       </c>
       <c r="N6" s="11">
-        <v>6452</v>
+        <v>5652</v>
       </c>
       <c r="O6" s="11">
-        <v>11557</v>
+        <v>2188</v>
       </c>
       <c r="P6" s="11">
-        <v>13711</v>
+        <v>6044</v>
       </c>
       <c r="Q6" s="11">
-        <v>9640</v>
+        <v>2374</v>
       </c>
       <c r="R6" s="11">
-        <v>1705</v>
+        <v>1482</v>
       </c>
       <c r="S6" s="11">
-        <v>8165</v>
+        <v>4314</v>
       </c>
       <c r="T6" s="12">
         <f>SUM(L6:S6)</f>
-        <v>66249</v>
+        <v>28788</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D7" s="9">
-        <v>33744</v>
+        <v>35173</v>
       </c>
       <c r="E7" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D7)/365.25,0)</f>
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H7" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L7" s="11">
-        <v>5474</v>
+        <v>12479</v>
       </c>
       <c r="M7" s="11">
-        <v>7328</v>
+        <v>7951</v>
       </c>
       <c r="N7" s="11">
-        <v>14340</v>
+        <v>2984</v>
       </c>
       <c r="O7" s="11">
-        <v>10558</v>
+        <v>2570</v>
       </c>
       <c r="P7" s="11">
-        <v>2042</v>
+        <v>7810</v>
       </c>
       <c r="Q7" s="11">
-        <v>7549</v>
+        <v>8281</v>
       </c>
       <c r="R7" s="11">
-        <v>13160</v>
+        <v>8239</v>
       </c>
       <c r="S7" s="11">
-        <v>13981</v>
+        <v>5365</v>
       </c>
       <c r="T7" s="12">
         <f>SUM(L7:S7)</f>
-        <v>74432</v>
+        <v>55679</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D8" s="9">
-        <v>35002</v>
+        <v>35490</v>
       </c>
       <c r="E8" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D8)/365.25,0)</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5">
         <v>3</v>
       </c>
-      <c r="H8" s="5">
-        <v>1</v>
-      </c>
       <c r="I8" s="5" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L8" s="11">
-        <v>4068</v>
+        <v>11995</v>
       </c>
       <c r="M8" s="11">
-        <v>8434</v>
+        <v>8801</v>
       </c>
       <c r="N8" s="11">
-        <v>14829</v>
+        <v>5937</v>
       </c>
       <c r="O8" s="11">
-        <v>13751</v>
+        <v>5672</v>
       </c>
       <c r="P8" s="11">
-        <v>9444</v>
+        <v>12185</v>
       </c>
       <c r="Q8" s="11">
-        <v>9589</v>
+        <v>5056</v>
       </c>
       <c r="R8" s="11">
-        <v>11954</v>
+        <v>13975</v>
       </c>
       <c r="S8" s="11">
-        <v>11257</v>
+        <v>13269</v>
       </c>
       <c r="T8" s="12">
         <f>SUM(L8:S8)</f>
-        <v>83326</v>
+        <v>76890</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>285</v>
+        <v>104</v>
       </c>
       <c r="D9" s="9">
-        <v>35173</v>
+        <v>38829</v>
       </c>
       <c r="E9" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D9)/365.25,0)</f>
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L9" s="11">
-        <v>12479</v>
+        <v>6753</v>
       </c>
       <c r="M9" s="11">
-        <v>7951</v>
+        <v>5038</v>
       </c>
       <c r="N9" s="11">
-        <v>2984</v>
+        <v>2552</v>
       </c>
       <c r="O9" s="11">
-        <v>2570</v>
+        <v>12887</v>
       </c>
       <c r="P9" s="11">
-        <v>7810</v>
+        <v>4761</v>
       </c>
       <c r="Q9" s="11">
-        <v>8281</v>
+        <v>9669</v>
       </c>
       <c r="R9" s="11">
-        <v>8239</v>
+        <v>4578</v>
       </c>
       <c r="S9" s="11">
-        <v>5365</v>
+        <v>10520</v>
       </c>
       <c r="T9" s="12">
         <f>SUM(L9:S9)</f>
-        <v>55679</v>
+        <v>56758</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="D10" s="9">
-        <v>35215</v>
+        <v>37903</v>
       </c>
       <c r="E10" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D10)/365.25,0)</f>
-        <v>28</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F10" s="10"/>
       <c r="G10" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H10" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>219</v>
+        <v>11</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L10" s="11">
-        <v>8262</v>
+        <v>10850</v>
       </c>
       <c r="M10" s="11">
-        <v>14390</v>
+        <v>4679</v>
       </c>
       <c r="N10" s="11">
-        <v>3074</v>
+        <v>12623</v>
       </c>
       <c r="O10" s="11">
-        <v>4101</v>
+        <v>8932</v>
       </c>
       <c r="P10" s="11">
-        <v>10107</v>
+        <v>1173</v>
       </c>
       <c r="Q10" s="11">
-        <v>7155</v>
+        <v>7187</v>
       </c>
       <c r="R10" s="11">
-        <v>14912</v>
+        <v>4370</v>
       </c>
       <c r="S10" s="11">
-        <v>6317</v>
+        <v>13426</v>
       </c>
       <c r="T10" s="12">
         <f>SUM(L10:S10)</f>
-        <v>68318</v>
+        <v>63240</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D11" s="9">
-        <v>35285</v>
+        <v>38648</v>
       </c>
       <c r="E11" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D11)/365.25,0)</f>
-        <v>28</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F11" s="10"/>
       <c r="G11" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="5">
         <v>1</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>219</v>
+        <v>17</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L11" s="11">
-        <v>6752</v>
+        <v>13904</v>
       </c>
       <c r="M11" s="11">
-        <v>9338</v>
+        <v>12606</v>
       </c>
       <c r="N11" s="11">
-        <v>8008</v>
+        <v>5378</v>
       </c>
       <c r="O11" s="11">
-        <v>8933</v>
+        <v>7573</v>
       </c>
       <c r="P11" s="11">
-        <v>10554</v>
+        <v>9260</v>
       </c>
       <c r="Q11" s="11">
-        <v>12164</v>
+        <v>14117</v>
       </c>
       <c r="R11" s="11">
-        <v>13676</v>
+        <v>4037</v>
       </c>
       <c r="S11" s="11">
-        <v>14242</v>
+        <v>11008</v>
       </c>
       <c r="T11" s="12">
         <f>SUM(L11:S11)</f>
-        <v>83667</v>
+        <v>77883</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D12" s="9">
-        <v>35488</v>
+        <v>36642</v>
       </c>
       <c r="E12" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D12)/365.25,0)</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H12" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L12" s="11">
-        <v>4714</v>
+        <v>2034</v>
       </c>
       <c r="M12" s="11">
-        <v>7955</v>
+        <v>2364</v>
       </c>
       <c r="N12" s="11">
-        <v>1956</v>
+        <v>5968</v>
       </c>
       <c r="O12" s="11">
-        <v>12954</v>
+        <v>11590</v>
       </c>
       <c r="P12" s="11">
-        <v>3266</v>
+        <v>11119</v>
       </c>
       <c r="Q12" s="11">
-        <v>6088</v>
+        <v>13309</v>
       </c>
       <c r="R12" s="11">
-        <v>12951</v>
+        <v>7222</v>
       </c>
       <c r="S12" s="11">
-        <v>12579</v>
+        <v>12275</v>
       </c>
       <c r="T12" s="12">
         <f>SUM(L12:S12)</f>
-        <v>62463</v>
+        <v>65881</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>103</v>
+        <v>286</v>
       </c>
       <c r="D13" s="9">
-        <v>35490</v>
+        <v>37179</v>
       </c>
       <c r="E13" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D13)/365.25,0)</f>
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="5" t="s">
@@ -4380,7 +4376,7 @@
         <v>3</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>11</v>
@@ -4389,1157 +4385,1162 @@
         <v>15</v>
       </c>
       <c r="L13" s="11">
-        <v>11995</v>
+        <v>10705</v>
       </c>
       <c r="M13" s="11">
-        <v>8801</v>
+        <v>13874</v>
       </c>
       <c r="N13" s="11">
-        <v>5937</v>
+        <v>5395</v>
       </c>
       <c r="O13" s="11">
-        <v>5672</v>
+        <v>1015</v>
       </c>
       <c r="P13" s="11">
-        <v>12185</v>
+        <v>12283</v>
       </c>
       <c r="Q13" s="11">
-        <v>5056</v>
+        <v>4259</v>
       </c>
       <c r="R13" s="11">
-        <v>13975</v>
+        <v>9307</v>
       </c>
       <c r="S13" s="11">
-        <v>13269</v>
+        <v>3806</v>
       </c>
       <c r="T13" s="12">
         <f>SUM(L13:S13)</f>
-        <v>76890</v>
+        <v>60644</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>156</v>
+        <v>108</v>
       </c>
       <c r="D14" s="9">
-        <v>35773</v>
+        <v>37196</v>
       </c>
       <c r="E14" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D14)/365.25,0)</f>
-        <v>27</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F14" s="10"/>
       <c r="G14" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="5">
         <v>3</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>220</v>
+        <v>11</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L14" s="11">
-        <v>10420</v>
+        <v>7248</v>
       </c>
       <c r="M14" s="11">
-        <v>13706</v>
+        <v>3275</v>
       </c>
       <c r="N14" s="11">
-        <v>8976</v>
+        <v>11781</v>
       </c>
       <c r="O14" s="11">
-        <v>5180</v>
+        <v>12629</v>
       </c>
       <c r="P14" s="11">
-        <v>12590</v>
+        <v>10785</v>
       </c>
       <c r="Q14" s="11">
-        <v>6698</v>
+        <v>5707</v>
       </c>
       <c r="R14" s="11">
-        <v>3975</v>
+        <v>5363</v>
       </c>
       <c r="S14" s="11">
-        <v>12042</v>
+        <v>6897</v>
       </c>
       <c r="T14" s="12">
         <f>SUM(L14:S14)</f>
-        <v>73587</v>
+        <v>63685</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="D15" s="9">
-        <v>35826</v>
+        <v>37348</v>
       </c>
       <c r="E15" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D15)/365.25,0)</f>
-        <v>27</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F15" s="10"/>
       <c r="G15" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="5">
         <v>1</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L15" s="11">
-        <v>7014</v>
+        <v>12244</v>
       </c>
       <c r="M15" s="11">
-        <v>8994</v>
+        <v>5924</v>
       </c>
       <c r="N15" s="11">
-        <v>10814</v>
+        <v>11878</v>
       </c>
       <c r="O15" s="11">
-        <v>4659</v>
+        <v>6507</v>
       </c>
       <c r="P15" s="11">
-        <v>12372</v>
+        <v>14299</v>
       </c>
       <c r="Q15" s="11">
-        <v>11193</v>
+        <v>5336</v>
       </c>
       <c r="R15" s="11">
-        <v>6944</v>
+        <v>10340</v>
       </c>
       <c r="S15" s="11">
-        <v>7433</v>
+        <v>1306</v>
       </c>
       <c r="T15" s="12">
         <f>SUM(L15:S15)</f>
-        <v>69423</v>
+        <v>67834</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D16" s="9">
-        <v>35855</v>
+        <v>37366</v>
       </c>
       <c r="E16" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D16)/365.25,0)</f>
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="5">
         <v>2</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L16" s="11">
-        <v>14240</v>
+        <v>7388</v>
       </c>
       <c r="M16" s="11">
-        <v>5496</v>
+        <v>13252</v>
       </c>
       <c r="N16" s="11">
-        <v>2026</v>
+        <v>8086</v>
       </c>
       <c r="O16" s="11">
-        <v>14172</v>
+        <v>12449</v>
       </c>
       <c r="P16" s="11">
-        <v>11389</v>
+        <v>6773</v>
       </c>
       <c r="Q16" s="11">
-        <v>5968</v>
+        <v>6821</v>
       </c>
       <c r="R16" s="11">
-        <v>11414</v>
+        <v>8276</v>
       </c>
       <c r="S16" s="11">
-        <v>3478</v>
+        <v>7906</v>
       </c>
       <c r="T16" s="12">
         <f>SUM(L16:S16)</f>
-        <v>68183</v>
+        <v>70951</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="D17" s="9">
-        <v>38451</v>
+        <v>37517</v>
       </c>
       <c r="E17" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D17)/365.25,0)</f>
-        <v>20</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F17" s="10"/>
       <c r="G17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" s="5">
         <v>3</v>
       </c>
-      <c r="H17" s="5">
-        <v>2</v>
-      </c>
       <c r="I17" s="5" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L17" s="11">
-        <v>5930</v>
+        <v>10349</v>
       </c>
       <c r="M17" s="11">
-        <v>5153</v>
+        <v>14002</v>
       </c>
       <c r="N17" s="11">
-        <v>2451</v>
+        <v>6490</v>
       </c>
       <c r="O17" s="11">
-        <v>13382</v>
+        <v>11615</v>
       </c>
       <c r="P17" s="11">
-        <v>7886</v>
+        <v>12493</v>
       </c>
       <c r="Q17" s="11">
-        <v>4364</v>
+        <v>7547</v>
       </c>
       <c r="R17" s="11">
-        <v>6723</v>
+        <v>7388</v>
       </c>
       <c r="S17" s="11">
-        <v>1441</v>
+        <v>5190</v>
       </c>
       <c r="T17" s="12">
         <f>SUM(L17:S17)</f>
-        <v>47330</v>
+        <v>75074</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D18" s="9">
-        <v>38829</v>
+        <v>37194</v>
       </c>
       <c r="E18" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D18)/365.25,0)</f>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L18" s="11">
-        <v>6753</v>
+        <v>10194</v>
       </c>
       <c r="M18" s="11">
-        <v>5038</v>
+        <v>10338</v>
       </c>
       <c r="N18" s="11">
-        <v>2552</v>
+        <v>14387</v>
       </c>
       <c r="O18" s="11">
-        <v>12887</v>
+        <v>3411</v>
       </c>
       <c r="P18" s="11">
-        <v>4761</v>
+        <v>7824</v>
       </c>
       <c r="Q18" s="11">
-        <v>9669</v>
+        <v>5811</v>
       </c>
       <c r="R18" s="11">
-        <v>4578</v>
+        <v>4372</v>
       </c>
       <c r="S18" s="11">
-        <v>10520</v>
+        <v>12928</v>
       </c>
       <c r="T18" s="12">
         <f>SUM(L18:S18)</f>
-        <v>56758</v>
+        <v>69265</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D19" s="9">
-        <v>39263</v>
+        <v>37232</v>
       </c>
       <c r="E19" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D19)/365.25,0)</f>
-        <v>17</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F19" s="10"/>
       <c r="G19" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H19" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>219</v>
+        <v>11</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L19" s="11">
-        <v>12501</v>
+        <v>10873</v>
       </c>
       <c r="M19" s="11">
-        <v>13192</v>
+        <v>11280</v>
       </c>
       <c r="N19" s="11">
-        <v>12243</v>
+        <v>11824</v>
       </c>
       <c r="O19" s="11">
-        <v>1410</v>
+        <v>1538</v>
       </c>
       <c r="P19" s="11">
-        <v>4145</v>
+        <v>2376</v>
       </c>
       <c r="Q19" s="11">
-        <v>4206</v>
+        <v>9456</v>
       </c>
       <c r="R19" s="11">
-        <v>1717</v>
+        <v>7948</v>
       </c>
       <c r="S19" s="11">
-        <v>12834</v>
+        <v>14935</v>
       </c>
       <c r="T19" s="12">
         <f>SUM(L19:S19)</f>
-        <v>62248</v>
+        <v>70230</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>284</v>
+        <v>114</v>
       </c>
       <c r="D20" s="9">
-        <v>35981</v>
+        <v>32527</v>
       </c>
       <c r="E20" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D20)/365.25,0)</f>
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="5">
         <v>2</v>
       </c>
-      <c r="H20" s="5">
-        <v>1</v>
-      </c>
       <c r="I20" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L20" s="11">
-        <v>1257</v>
+        <v>5984</v>
       </c>
       <c r="M20" s="11">
-        <v>5570</v>
+        <v>14769</v>
       </c>
       <c r="N20" s="11">
-        <v>5070</v>
+        <v>10766</v>
       </c>
       <c r="O20" s="11">
-        <v>8444</v>
+        <v>9915</v>
       </c>
       <c r="P20" s="11">
-        <v>10627</v>
+        <v>12892</v>
       </c>
       <c r="Q20" s="11">
-        <v>10242</v>
+        <v>1840</v>
       </c>
       <c r="R20" s="11">
-        <v>13650</v>
+        <v>4402</v>
       </c>
       <c r="S20" s="11">
-        <v>14082</v>
+        <v>3825</v>
       </c>
       <c r="T20" s="12">
         <f>SUM(L20:S20)</f>
-        <v>68942</v>
+        <v>64393</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D21" s="9">
-        <v>36055</v>
+        <v>35002</v>
       </c>
       <c r="E21" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D21)/365.25,0)</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L21" s="11">
-        <v>5152</v>
+        <v>4068</v>
       </c>
       <c r="M21" s="11">
-        <v>1582</v>
+        <v>8434</v>
       </c>
       <c r="N21" s="11">
-        <v>5652</v>
+        <v>14829</v>
       </c>
       <c r="O21" s="11">
-        <v>2188</v>
+        <v>13751</v>
       </c>
       <c r="P21" s="11">
-        <v>6044</v>
+        <v>9444</v>
       </c>
       <c r="Q21" s="11">
-        <v>2374</v>
+        <v>9589</v>
       </c>
       <c r="R21" s="11">
-        <v>1482</v>
+        <v>11954</v>
       </c>
       <c r="S21" s="11">
-        <v>4314</v>
+        <v>11257</v>
       </c>
       <c r="T21" s="12">
         <f>SUM(L21:S21)</f>
-        <v>28788</v>
+        <v>83326</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D22" s="9">
-        <v>38616</v>
+        <v>35855</v>
       </c>
       <c r="E22" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D22)/365.25,0)</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="5">
         <v>2</v>
       </c>
-      <c r="H22" s="5">
-        <v>3</v>
-      </c>
       <c r="I22" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L22" s="11">
-        <v>6797</v>
+        <v>14240</v>
       </c>
       <c r="M22" s="11">
-        <v>11582</v>
+        <v>5496</v>
       </c>
       <c r="N22" s="11">
-        <v>12324</v>
+        <v>2026</v>
       </c>
       <c r="O22" s="11">
-        <v>4594</v>
+        <v>14172</v>
       </c>
       <c r="P22" s="11">
-        <v>12737</v>
+        <v>11389</v>
       </c>
       <c r="Q22" s="11">
-        <v>10934</v>
+        <v>5968</v>
       </c>
       <c r="R22" s="11">
-        <v>14077</v>
+        <v>11414</v>
       </c>
       <c r="S22" s="11">
-        <v>12988</v>
+        <v>3478</v>
       </c>
       <c r="T22" s="12">
         <f>SUM(L22:S22)</f>
-        <v>86033</v>
+        <v>68183</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D23" s="9">
-        <v>39059</v>
+        <v>38616</v>
       </c>
       <c r="E23" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D23)/365.25,0)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" s="5">
         <v>3</v>
       </c>
-      <c r="H23" s="5">
-        <v>2</v>
-      </c>
       <c r="I23" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L23" s="11">
-        <v>2903</v>
+        <v>6797</v>
       </c>
       <c r="M23" s="11">
-        <v>13361</v>
+        <v>11582</v>
       </c>
       <c r="N23" s="11">
-        <v>3297</v>
+        <v>12324</v>
       </c>
       <c r="O23" s="11">
-        <v>1010</v>
+        <v>4594</v>
       </c>
       <c r="P23" s="11">
-        <v>13958</v>
+        <v>12737</v>
       </c>
       <c r="Q23" s="11">
-        <v>1602</v>
+        <v>10934</v>
       </c>
       <c r="R23" s="11">
-        <v>4926</v>
+        <v>14077</v>
       </c>
       <c r="S23" s="11">
-        <v>10012</v>
+        <v>12988</v>
       </c>
       <c r="T23" s="12">
         <f>SUM(L23:S23)</f>
-        <v>51069</v>
+        <v>86033</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D24" s="9">
-        <v>36177</v>
+        <v>39059</v>
       </c>
       <c r="E24" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D24)/365.25,0)</f>
-        <v>26</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F24" s="10"/>
       <c r="G24" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H24" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L24" s="11">
-        <v>12842</v>
+        <v>2903</v>
       </c>
       <c r="M24" s="11">
-        <v>14209</v>
+        <v>13361</v>
       </c>
       <c r="N24" s="11">
-        <v>12919</v>
+        <v>3297</v>
       </c>
       <c r="O24" s="11">
-        <v>7812</v>
+        <v>1010</v>
       </c>
       <c r="P24" s="11">
-        <v>3380</v>
+        <v>13958</v>
       </c>
       <c r="Q24" s="11">
-        <v>12767</v>
+        <v>1602</v>
       </c>
       <c r="R24" s="11">
-        <v>8848</v>
+        <v>4926</v>
       </c>
       <c r="S24" s="11">
-        <v>13617</v>
+        <v>10012</v>
       </c>
       <c r="T24" s="12">
         <f>SUM(L24:S24)</f>
-        <v>86394</v>
+        <v>51069</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D25" s="9">
-        <v>39180</v>
+        <v>36385</v>
       </c>
       <c r="E25" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D25)/365.25,0)</f>
-        <v>18</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F25" s="10"/>
       <c r="G25" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H25" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>13</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L25" s="11">
-        <v>9823</v>
+        <v>9328</v>
       </c>
       <c r="M25" s="11">
-        <v>3238</v>
+        <v>6134</v>
       </c>
       <c r="N25" s="11">
-        <v>8111</v>
+        <v>1890</v>
       </c>
       <c r="O25" s="11">
-        <v>2537</v>
+        <v>7897</v>
       </c>
       <c r="P25" s="11">
-        <v>12217</v>
+        <v>10122</v>
       </c>
       <c r="Q25" s="11">
-        <v>1306</v>
+        <v>8195</v>
       </c>
       <c r="R25" s="11">
-        <v>11759</v>
+        <v>5366</v>
       </c>
       <c r="S25" s="11">
-        <v>8920</v>
+        <v>12826</v>
       </c>
       <c r="T25" s="12">
         <f>SUM(L25:S25)</f>
-        <v>57911</v>
+        <v>61758</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="D26" s="9">
-        <v>36265</v>
+        <v>37031</v>
       </c>
       <c r="E26" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D26)/365.25,0)</f>
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F26" s="10"/>
       <c r="G26" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H26" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L26" s="11">
-        <v>3392</v>
+        <v>13690</v>
       </c>
       <c r="M26" s="11">
-        <v>3879</v>
+        <v>3859</v>
       </c>
       <c r="N26" s="11">
-        <v>9397</v>
+        <v>7411</v>
       </c>
       <c r="O26" s="11">
-        <v>7101</v>
+        <v>3490</v>
       </c>
       <c r="P26" s="11">
-        <v>1967</v>
+        <v>9006</v>
       </c>
       <c r="Q26" s="11">
-        <v>2627</v>
+        <v>4862</v>
       </c>
       <c r="R26" s="11">
-        <v>3572</v>
+        <v>9580</v>
       </c>
       <c r="S26" s="11">
-        <v>2759</v>
+        <v>7654</v>
       </c>
       <c r="T26" s="12">
         <f>SUM(L26:S26)</f>
-        <v>34694</v>
+        <v>59552</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="D27" s="9">
-        <v>36274</v>
+        <v>37357</v>
       </c>
       <c r="E27" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D27)/365.25,0)</f>
-        <v>26</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F27" s="10"/>
       <c r="G27" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="5">
         <v>3</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L27" s="11">
-        <v>14919</v>
+        <v>13086</v>
       </c>
       <c r="M27" s="11">
-        <v>12023</v>
+        <v>5443</v>
       </c>
       <c r="N27" s="11">
-        <v>2203</v>
+        <v>6273</v>
       </c>
       <c r="O27" s="11">
-        <v>4964</v>
+        <v>9954</v>
       </c>
       <c r="P27" s="11">
-        <v>8231</v>
+        <v>10103</v>
       </c>
       <c r="Q27" s="11">
-        <v>9821</v>
+        <v>11905</v>
       </c>
       <c r="R27" s="11">
-        <v>4590</v>
+        <v>12906</v>
       </c>
       <c r="S27" s="11">
-        <v>1506</v>
+        <v>6207</v>
       </c>
       <c r="T27" s="12">
         <f>SUM(L27:S27)</f>
-        <v>58257</v>
+        <v>75877</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D28" s="9">
-        <v>36385</v>
+        <v>35285</v>
       </c>
       <c r="E28" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D28)/365.25,0)</f>
-        <v>25</v>
-      </c>
-      <c r="F28" s="10"/>
+        <v>29</v>
+      </c>
       <c r="G28" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>13</v>
+        <v>219</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L28" s="11">
-        <v>9328</v>
+        <v>6752</v>
       </c>
       <c r="M28" s="11">
-        <v>6134</v>
+        <v>9338</v>
       </c>
       <c r="N28" s="11">
-        <v>1890</v>
+        <v>8008</v>
       </c>
       <c r="O28" s="11">
-        <v>7897</v>
+        <v>8933</v>
       </c>
       <c r="P28" s="11">
-        <v>10122</v>
+        <v>10554</v>
       </c>
       <c r="Q28" s="11">
-        <v>8195</v>
+        <v>12164</v>
       </c>
       <c r="R28" s="11">
-        <v>5366</v>
+        <v>13676</v>
       </c>
       <c r="S28" s="11">
-        <v>12826</v>
+        <v>14242</v>
       </c>
       <c r="T28" s="12">
         <f>SUM(L28:S28)</f>
-        <v>61758</v>
+        <v>83667</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="D29" s="9">
-        <v>36393</v>
+        <v>36704</v>
       </c>
       <c r="E29" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D29)/365.25,0)</f>
         <v>25</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="5">
         <v>2</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>220</v>
+        <v>11</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L29" s="11">
-        <v>3064</v>
+        <v>9012</v>
       </c>
       <c r="M29" s="11">
-        <v>9829</v>
+        <v>7352</v>
       </c>
       <c r="N29" s="11">
-        <v>5005</v>
+        <v>9751</v>
       </c>
       <c r="O29" s="11">
-        <v>1772</v>
+        <v>10298</v>
       </c>
       <c r="P29" s="11">
-        <v>12445</v>
+        <v>1213</v>
       </c>
       <c r="Q29" s="11">
-        <v>8675</v>
+        <v>13376</v>
       </c>
       <c r="R29" s="11">
-        <v>11988</v>
+        <v>6059</v>
       </c>
       <c r="S29" s="11">
-        <v>10020</v>
+        <v>7818</v>
       </c>
       <c r="T29" s="12">
         <f>SUM(L29:S29)</f>
-        <v>62798</v>
+        <v>64879</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D30" s="9">
-        <v>37903</v>
+        <v>36707</v>
       </c>
       <c r="E30" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D30)/365.25,0)</f>
-        <v>21</v>
-      </c>
-      <c r="F30" s="10"/>
+        <v>25</v>
+      </c>
       <c r="G30" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H30" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L30" s="11">
-        <v>10850</v>
+        <v>6097</v>
       </c>
       <c r="M30" s="11">
-        <v>4679</v>
+        <v>1039</v>
       </c>
       <c r="N30" s="11">
-        <v>12623</v>
+        <v>7783</v>
       </c>
       <c r="O30" s="11">
-        <v>8932</v>
+        <v>6873</v>
       </c>
       <c r="P30" s="11">
-        <v>1173</v>
+        <v>10127</v>
       </c>
       <c r="Q30" s="11">
-        <v>7187</v>
+        <v>12633</v>
       </c>
       <c r="R30" s="11">
-        <v>4370</v>
+        <v>11573</v>
       </c>
       <c r="S30" s="11">
-        <v>13426</v>
+        <v>13399</v>
       </c>
       <c r="T30" s="12">
         <f>SUM(L30:S30)</f>
-        <v>63240</v>
+        <v>69524</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="D31" s="9">
-        <v>38648</v>
+        <v>37070</v>
       </c>
       <c r="E31" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D31)/365.25,0)</f>
-        <v>19</v>
-      </c>
-      <c r="F31" s="10"/>
+        <v>24</v>
+      </c>
       <c r="G31" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H31" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L31" s="11">
-        <v>13904</v>
+        <v>5516</v>
       </c>
       <c r="M31" s="11">
-        <v>12606</v>
+        <v>7942</v>
       </c>
       <c r="N31" s="11">
-        <v>5378</v>
+        <v>12821</v>
       </c>
       <c r="O31" s="11">
-        <v>7573</v>
+        <v>2235</v>
       </c>
       <c r="P31" s="11">
-        <v>9260</v>
+        <v>7581</v>
       </c>
       <c r="Q31" s="11">
-        <v>14117</v>
+        <v>3488</v>
       </c>
       <c r="R31" s="11">
-        <v>4037</v>
+        <v>10523</v>
       </c>
       <c r="S31" s="11">
-        <v>11008</v>
+        <v>11825</v>
       </c>
       <c r="T31" s="12">
         <f>SUM(L31:S31)</f>
-        <v>77883</v>
+        <v>61931</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D32" s="9">
-        <v>39019</v>
+        <v>29443</v>
       </c>
       <c r="E32" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D32)/365.25,0)</f>
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>2</v>
@@ -5548,59 +5549,59 @@
         <v>3</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L32" s="11">
-        <v>3155</v>
+        <v>1276</v>
       </c>
       <c r="M32" s="11">
-        <v>2959</v>
+        <v>13202</v>
       </c>
       <c r="N32" s="11">
-        <v>1380</v>
+        <v>3858</v>
       </c>
       <c r="O32" s="11">
-        <v>2202</v>
+        <v>14009</v>
       </c>
       <c r="P32" s="11">
-        <v>13546</v>
+        <v>8824</v>
       </c>
       <c r="Q32" s="11">
-        <v>4631</v>
+        <v>5508</v>
       </c>
       <c r="R32" s="11">
-        <v>5953</v>
+        <v>3519</v>
       </c>
       <c r="S32" s="11">
-        <v>8922</v>
+        <v>14895</v>
       </c>
       <c r="T32" s="12">
         <f>SUM(L32:S32)</f>
-        <v>42748</v>
+        <v>65091</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D33" s="9">
-        <v>39426</v>
+        <v>33703</v>
       </c>
       <c r="E33" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D33)/365.25,0)</f>
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>2</v>
@@ -5609,557 +5610,556 @@
         <v>3</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>11</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L33" s="11">
-        <v>12227</v>
+        <v>1200</v>
       </c>
       <c r="M33" s="11">
-        <v>2589</v>
+        <v>13819</v>
       </c>
       <c r="N33" s="11">
-        <v>2480</v>
+        <v>6452</v>
       </c>
       <c r="O33" s="11">
-        <v>11661</v>
+        <v>11557</v>
       </c>
       <c r="P33" s="11">
-        <v>5115</v>
+        <v>13711</v>
       </c>
       <c r="Q33" s="11">
-        <v>13509</v>
+        <v>9640</v>
       </c>
       <c r="R33" s="11">
-        <v>13344</v>
+        <v>1705</v>
       </c>
       <c r="S33" s="11">
-        <v>9160</v>
+        <v>8165</v>
       </c>
       <c r="T33" s="12">
         <f>SUM(L33:S33)</f>
-        <v>70085</v>
+        <v>66249</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D34" s="9">
-        <v>36543</v>
+        <v>39263</v>
       </c>
       <c r="E34" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D34)/365.25,0)</f>
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H34" s="5">
         <v>3</v>
       </c>
-      <c r="H34" s="5">
-        <v>2</v>
-      </c>
       <c r="I34" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L34" s="11">
-        <v>13910</v>
+        <v>12501</v>
       </c>
       <c r="M34" s="11">
-        <v>11243</v>
+        <v>13192</v>
       </c>
       <c r="N34" s="11">
-        <v>3878</v>
+        <v>12243</v>
       </c>
       <c r="O34" s="11">
-        <v>3379</v>
+        <v>1410</v>
       </c>
       <c r="P34" s="11">
-        <v>1980</v>
+        <v>4145</v>
       </c>
       <c r="Q34" s="11">
-        <v>8419</v>
+        <v>4206</v>
       </c>
       <c r="R34" s="11">
-        <v>9880</v>
+        <v>1717</v>
       </c>
       <c r="S34" s="11">
-        <v>12023</v>
+        <v>12834</v>
       </c>
       <c r="T34" s="12">
         <f>SUM(L34:S34)</f>
-        <v>64712</v>
+        <v>62248</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="D35" s="9">
-        <v>36642</v>
+        <v>36177</v>
       </c>
       <c r="E35" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D35)/365.25,0)</f>
-        <v>25</v>
-      </c>
-      <c r="F35" s="10"/>
+        <v>26</v>
+      </c>
       <c r="G35" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L35" s="11">
-        <v>2034</v>
+        <v>12842</v>
       </c>
       <c r="M35" s="11">
-        <v>2364</v>
+        <v>14209</v>
       </c>
       <c r="N35" s="11">
-        <v>5968</v>
+        <v>12919</v>
       </c>
       <c r="O35" s="11">
-        <v>11590</v>
+        <v>7812</v>
       </c>
       <c r="P35" s="11">
-        <v>11119</v>
+        <v>3380</v>
       </c>
       <c r="Q35" s="11">
-        <v>13309</v>
+        <v>12767</v>
       </c>
       <c r="R35" s="11">
-        <v>7222</v>
+        <v>8848</v>
       </c>
       <c r="S35" s="11">
-        <v>12275</v>
+        <v>13617</v>
       </c>
       <c r="T35" s="12">
         <f>SUM(L35:S35)</f>
-        <v>65881</v>
+        <v>86394</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D36" s="9">
-        <v>36664</v>
+        <v>39019</v>
       </c>
       <c r="E36" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D36)/365.25,0)</f>
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H36" s="5">
         <v>3</v>
       </c>
-      <c r="H36" s="5">
-        <v>1</v>
-      </c>
       <c r="I36" s="5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L36" s="11">
-        <v>13182</v>
+        <v>3155</v>
       </c>
       <c r="M36" s="11">
-        <v>6465</v>
+        <v>2959</v>
       </c>
       <c r="N36" s="11">
-        <v>4952</v>
+        <v>1380</v>
       </c>
       <c r="O36" s="11">
-        <v>6789</v>
+        <v>2202</v>
       </c>
       <c r="P36" s="11">
-        <v>7607</v>
+        <v>13546</v>
       </c>
       <c r="Q36" s="11">
-        <v>14190</v>
+        <v>4631</v>
       </c>
       <c r="R36" s="11">
-        <v>10895</v>
+        <v>5953</v>
       </c>
       <c r="S36" s="11">
-        <v>12822</v>
+        <v>8922</v>
       </c>
       <c r="T36" s="12">
         <f>SUM(L36:S36)</f>
-        <v>76902</v>
+        <v>42748</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D37" s="9">
-        <v>36704</v>
+        <v>36948</v>
       </c>
       <c r="E37" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D37)/365.25,0)</f>
         <v>24</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L37" s="11">
-        <v>9012</v>
+        <v>2161</v>
       </c>
       <c r="M37" s="11">
-        <v>7352</v>
+        <v>6678</v>
       </c>
       <c r="N37" s="11">
-        <v>9751</v>
+        <v>11295</v>
       </c>
       <c r="O37" s="11">
-        <v>10298</v>
+        <v>2730</v>
       </c>
       <c r="P37" s="11">
-        <v>1213</v>
+        <v>8504</v>
       </c>
       <c r="Q37" s="11">
-        <v>13376</v>
+        <v>3075</v>
       </c>
       <c r="R37" s="11">
-        <v>6059</v>
+        <v>11758</v>
       </c>
       <c r="S37" s="11">
-        <v>7818</v>
+        <v>4345</v>
       </c>
       <c r="T37" s="12">
         <f>SUM(L37:S37)</f>
-        <v>64879</v>
+        <v>50546</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D38" s="9">
-        <v>36707</v>
+        <v>37191</v>
       </c>
       <c r="E38" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D38)/365.25,0)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H38" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L38" s="11">
-        <v>6097</v>
+        <v>5067</v>
       </c>
       <c r="M38" s="11">
-        <v>1039</v>
+        <v>6498</v>
       </c>
       <c r="N38" s="11">
-        <v>7783</v>
+        <v>6279</v>
       </c>
       <c r="O38" s="11">
-        <v>6873</v>
+        <v>10224</v>
       </c>
       <c r="P38" s="11">
-        <v>10127</v>
+        <v>4929</v>
       </c>
       <c r="Q38" s="11">
-        <v>12633</v>
+        <v>10101</v>
       </c>
       <c r="R38" s="11">
-        <v>11573</v>
+        <v>3231</v>
       </c>
       <c r="S38" s="11">
-        <v>13399</v>
+        <v>6141</v>
       </c>
       <c r="T38" s="12">
         <f>SUM(L38:S38)</f>
-        <v>69524</v>
+        <v>52470</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="D39" s="9">
-        <v>36712</v>
+        <v>39426</v>
       </c>
       <c r="E39" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D39)/365.25,0)</f>
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H39" s="5">
         <v>3</v>
       </c>
-      <c r="H39" s="5">
-        <v>2</v>
-      </c>
       <c r="I39" s="5" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>11</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L39" s="11">
-        <v>11482</v>
+        <v>12227</v>
       </c>
       <c r="M39" s="11">
-        <v>6887</v>
+        <v>2589</v>
       </c>
       <c r="N39" s="11">
-        <v>7380</v>
+        <v>2480</v>
       </c>
       <c r="O39" s="11">
-        <v>9248</v>
+        <v>11661</v>
       </c>
       <c r="P39" s="11">
-        <v>4854</v>
+        <v>5115</v>
       </c>
       <c r="Q39" s="11">
-        <v>4576</v>
+        <v>13509</v>
       </c>
       <c r="R39" s="11">
-        <v>6977</v>
+        <v>13344</v>
       </c>
       <c r="S39" s="11">
-        <v>12270</v>
+        <v>9160</v>
       </c>
       <c r="T39" s="12">
         <f>SUM(L39:S39)</f>
-        <v>63674</v>
+        <v>70085</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D40" s="9">
-        <v>36745</v>
+        <v>33014</v>
       </c>
       <c r="E40" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D40)/365.25,0)</f>
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H40" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>13</v>
+        <v>219</v>
       </c>
       <c r="K40" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L40" s="11">
-        <v>10532</v>
+        <v>7735</v>
       </c>
       <c r="M40" s="11">
-        <v>14287</v>
+        <v>3896</v>
       </c>
       <c r="N40" s="11">
-        <v>1712</v>
+        <v>7631</v>
       </c>
       <c r="O40" s="11">
-        <v>4789</v>
+        <v>2919</v>
       </c>
       <c r="P40" s="11">
-        <v>2709</v>
+        <v>3155</v>
       </c>
       <c r="Q40" s="11">
-        <v>2977</v>
+        <v>10681</v>
       </c>
       <c r="R40" s="11">
-        <v>8390</v>
+        <v>7483</v>
       </c>
       <c r="S40" s="11">
-        <v>1113</v>
+        <v>2514</v>
       </c>
       <c r="T40" s="12">
         <f>SUM(L40:S40)</f>
-        <v>46509</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D41" s="9">
-        <v>36840</v>
+        <v>38005</v>
       </c>
       <c r="E41" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D41)/365.25,0)</f>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>219</v>
+        <v>11</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L41" s="11">
-        <v>14072</v>
+        <v>11765</v>
       </c>
       <c r="M41" s="11">
-        <v>14620</v>
+        <v>9493</v>
       </c>
       <c r="N41" s="11">
-        <v>4735</v>
+        <v>4483</v>
       </c>
       <c r="O41" s="11">
-        <v>8710</v>
+        <v>11577</v>
       </c>
       <c r="P41" s="11">
-        <v>4442</v>
+        <v>4989</v>
       </c>
       <c r="Q41" s="11">
-        <v>14601</v>
+        <v>6670</v>
       </c>
       <c r="R41" s="11">
-        <v>13322</v>
+        <v>4199</v>
       </c>
       <c r="S41" s="11">
-        <v>3703</v>
+        <v>7638</v>
       </c>
       <c r="T41" s="12">
         <f>SUM(L41:S41)</f>
-        <v>78205</v>
+        <v>60814</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D42" s="9">
-        <v>36948</v>
+        <v>38451</v>
       </c>
       <c r="E42" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D42)/365.25,0)</f>
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G42" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="5">
         <v>2</v>
       </c>
-      <c r="H42" s="5">
-        <v>1</v>
-      </c>
       <c r="I42" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J42" s="9" t="s">
         <v>13</v>
@@ -6168,50 +6168,50 @@
         <v>15</v>
       </c>
       <c r="L42" s="11">
-        <v>2161</v>
+        <v>5930</v>
       </c>
       <c r="M42" s="11">
-        <v>6678</v>
+        <v>5153</v>
       </c>
       <c r="N42" s="11">
-        <v>11295</v>
+        <v>2451</v>
       </c>
       <c r="O42" s="11">
-        <v>2730</v>
+        <v>13382</v>
       </c>
       <c r="P42" s="11">
-        <v>8504</v>
+        <v>7886</v>
       </c>
       <c r="Q42" s="11">
-        <v>3075</v>
+        <v>4364</v>
       </c>
       <c r="R42" s="11">
-        <v>11758</v>
+        <v>6723</v>
       </c>
       <c r="S42" s="11">
-        <v>4345</v>
+        <v>1441</v>
       </c>
       <c r="T42" s="12">
         <f>SUM(L42:S42)</f>
-        <v>50546</v>
+        <v>47330</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D43" s="9">
-        <v>36958</v>
+        <v>32000</v>
       </c>
       <c r="E43" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D43)/365.25,0)</f>
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>2</v>
@@ -6220,130 +6220,129 @@
         <v>3</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L43" s="11">
-        <v>7751</v>
+        <v>13010</v>
       </c>
       <c r="M43" s="11">
-        <v>4810</v>
+        <v>8535</v>
       </c>
       <c r="N43" s="11">
-        <v>6694</v>
+        <v>5678</v>
       </c>
       <c r="O43" s="11">
-        <v>8552</v>
+        <v>13717</v>
       </c>
       <c r="P43" s="11">
-        <v>14526</v>
+        <v>2821</v>
       </c>
       <c r="Q43" s="11">
-        <v>6687</v>
+        <v>4343</v>
       </c>
       <c r="R43" s="11">
-        <v>12321</v>
+        <v>1832</v>
       </c>
       <c r="S43" s="11">
-        <v>9920</v>
+        <v>7942</v>
       </c>
       <c r="T43" s="12">
         <f>SUM(L43:S43)</f>
-        <v>71261</v>
+        <v>57878</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D44" s="9">
-        <v>37029</v>
+        <v>36543</v>
       </c>
       <c r="E44" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D44)/365.25,0)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" s="5">
         <v>2</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>11</v>
+        <v>220</v>
       </c>
       <c r="K44" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L44" s="11">
-        <v>14656</v>
+        <v>13910</v>
       </c>
       <c r="M44" s="11">
-        <v>10828</v>
+        <v>11243</v>
       </c>
       <c r="N44" s="11">
-        <v>7927</v>
+        <v>3878</v>
       </c>
       <c r="O44" s="11">
-        <v>8647</v>
+        <v>3379</v>
       </c>
       <c r="P44" s="11">
-        <v>10760</v>
+        <v>1980</v>
       </c>
       <c r="Q44" s="11">
-        <v>2441</v>
+        <v>8419</v>
       </c>
       <c r="R44" s="11">
-        <v>7360</v>
+        <v>9880</v>
       </c>
       <c r="S44" s="11">
-        <v>9385</v>
+        <v>12023</v>
       </c>
       <c r="T44" s="12">
         <f>SUM(L44:S44)</f>
-        <v>72004</v>
+        <v>64712</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D45" s="9">
-        <v>37031</v>
+        <v>36664</v>
       </c>
       <c r="E45" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D45)/365.25,0)</f>
-        <v>24</v>
-      </c>
-      <c r="F45" s="10"/>
+        <v>25</v>
+      </c>
       <c r="G45" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>11</v>
@@ -6352,297 +6351,295 @@
         <v>15</v>
       </c>
       <c r="L45" s="11">
-        <v>13690</v>
+        <v>13182</v>
       </c>
       <c r="M45" s="11">
-        <v>3859</v>
+        <v>6465</v>
       </c>
       <c r="N45" s="11">
-        <v>7411</v>
+        <v>4952</v>
       </c>
       <c r="O45" s="11">
-        <v>3490</v>
+        <v>6789</v>
       </c>
       <c r="P45" s="11">
-        <v>9006</v>
+        <v>7607</v>
       </c>
       <c r="Q45" s="11">
-        <v>4862</v>
+        <v>14190</v>
       </c>
       <c r="R45" s="11">
-        <v>9580</v>
+        <v>10895</v>
       </c>
       <c r="S45" s="11">
-        <v>7654</v>
+        <v>12822</v>
       </c>
       <c r="T45" s="12">
         <f>SUM(L45:S45)</f>
-        <v>59552</v>
+        <v>76902</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="D46" s="9">
-        <v>37070</v>
+        <v>35215</v>
       </c>
       <c r="E46" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D46)/365.25,0)</f>
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>13</v>
+        <v>219</v>
       </c>
       <c r="K46" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L46" s="11">
-        <v>5516</v>
+        <v>8262</v>
       </c>
       <c r="M46" s="11">
-        <v>7942</v>
+        <v>14390</v>
       </c>
       <c r="N46" s="11">
-        <v>12821</v>
+        <v>3074</v>
       </c>
       <c r="O46" s="11">
-        <v>2235</v>
+        <v>4101</v>
       </c>
       <c r="P46" s="11">
-        <v>7581</v>
+        <v>10107</v>
       </c>
       <c r="Q46" s="11">
-        <v>3488</v>
+        <v>7155</v>
       </c>
       <c r="R46" s="11">
-        <v>10523</v>
+        <v>14912</v>
       </c>
       <c r="S46" s="11">
-        <v>11825</v>
+        <v>6317</v>
       </c>
       <c r="T46" s="12">
         <f>SUM(L46:S46)</f>
-        <v>61931</v>
+        <v>68318</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D47" s="9">
-        <v>37159</v>
+        <v>35826</v>
       </c>
       <c r="E47" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D47)/365.25,0)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H47" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K47" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L47" s="11">
-        <v>9902</v>
+        <v>7014</v>
       </c>
       <c r="M47" s="11">
-        <v>13690</v>
+        <v>8994</v>
       </c>
       <c r="N47" s="11">
-        <v>7185</v>
+        <v>10814</v>
       </c>
       <c r="O47" s="11">
-        <v>11873</v>
+        <v>4659</v>
       </c>
       <c r="P47" s="11">
-        <v>10257</v>
+        <v>12372</v>
       </c>
       <c r="Q47" s="11">
-        <v>1153</v>
+        <v>11193</v>
       </c>
       <c r="R47" s="11">
-        <v>14091</v>
+        <v>6944</v>
       </c>
       <c r="S47" s="11">
-        <v>7430</v>
+        <v>7433</v>
       </c>
       <c r="T47" s="12">
         <f>SUM(L47:S47)</f>
-        <v>75581</v>
+        <v>69423</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>286</v>
+        <v>142</v>
       </c>
       <c r="D48" s="9">
-        <v>37179</v>
+        <v>36265</v>
       </c>
       <c r="E48" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D48)/365.25,0)</f>
-        <v>23</v>
-      </c>
-      <c r="F48" s="10"/>
+        <v>26</v>
+      </c>
       <c r="G48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H48" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L48" s="11">
-        <v>10705</v>
+        <v>3392</v>
       </c>
       <c r="M48" s="11">
-        <v>13874</v>
+        <v>3879</v>
       </c>
       <c r="N48" s="11">
-        <v>5395</v>
+        <v>9397</v>
       </c>
       <c r="O48" s="11">
-        <v>1015</v>
+        <v>7101</v>
       </c>
       <c r="P48" s="11">
-        <v>12283</v>
+        <v>1967</v>
       </c>
       <c r="Q48" s="11">
-        <v>4259</v>
+        <v>2627</v>
       </c>
       <c r="R48" s="11">
-        <v>9307</v>
+        <v>3572</v>
       </c>
       <c r="S48" s="11">
-        <v>3806</v>
+        <v>2759</v>
       </c>
       <c r="T48" s="12">
         <f>SUM(L48:S48)</f>
-        <v>60644</v>
+        <v>34694</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="D49" s="9">
-        <v>37191</v>
+        <v>36274</v>
       </c>
       <c r="E49" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D49)/365.25,0)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K49" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L49" s="11">
-        <v>5067</v>
+        <v>14919</v>
       </c>
       <c r="M49" s="11">
-        <v>6498</v>
+        <v>12023</v>
       </c>
       <c r="N49" s="11">
-        <v>6279</v>
+        <v>2203</v>
       </c>
       <c r="O49" s="11">
-        <v>10224</v>
+        <v>4964</v>
       </c>
       <c r="P49" s="11">
-        <v>4929</v>
+        <v>8231</v>
       </c>
       <c r="Q49" s="11">
-        <v>10101</v>
+        <v>9821</v>
       </c>
       <c r="R49" s="11">
-        <v>3231</v>
+        <v>4590</v>
       </c>
       <c r="S49" s="11">
-        <v>6141</v>
+        <v>1506</v>
       </c>
       <c r="T49" s="12">
         <f>SUM(L49:S49)</f>
-        <v>52470</v>
+        <v>58257</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="D50" s="9">
-        <v>37194</v>
+        <v>36393</v>
       </c>
       <c r="E50" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D50)/365.25,0)</f>
-        <v>23</v>
-      </c>
-      <c r="F50" s="10"/>
+        <v>26</v>
+      </c>
       <c r="G50" s="5" t="s">
         <v>2</v>
       </c>
@@ -6650,122 +6647,121 @@
         <v>2</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>10</v>
+        <v>220</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L50" s="11">
-        <v>10194</v>
+        <v>3064</v>
       </c>
       <c r="M50" s="11">
-        <v>10338</v>
+        <v>9829</v>
       </c>
       <c r="N50" s="11">
-        <v>14387</v>
+        <v>5005</v>
       </c>
       <c r="O50" s="11">
-        <v>3411</v>
+        <v>1772</v>
       </c>
       <c r="P50" s="11">
-        <v>7824</v>
+        <v>12445</v>
       </c>
       <c r="Q50" s="11">
-        <v>5811</v>
+        <v>8675</v>
       </c>
       <c r="R50" s="11">
-        <v>4372</v>
+        <v>11988</v>
       </c>
       <c r="S50" s="11">
-        <v>12928</v>
+        <v>10020</v>
       </c>
       <c r="T50" s="12">
         <f>SUM(L50:S50)</f>
-        <v>69265</v>
+        <v>62798</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D51" s="9">
-        <v>37195</v>
+        <v>36712</v>
       </c>
       <c r="E51" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D51)/365.25,0)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H51" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K51" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L51" s="11">
-        <v>13971</v>
+        <v>11482</v>
       </c>
       <c r="M51" s="11">
-        <v>1233</v>
+        <v>6887</v>
       </c>
       <c r="N51" s="11">
-        <v>2339</v>
+        <v>7380</v>
       </c>
       <c r="O51" s="11">
-        <v>2920</v>
+        <v>9248</v>
       </c>
       <c r="P51" s="11">
-        <v>2949</v>
+        <v>4854</v>
       </c>
       <c r="Q51" s="11">
-        <v>8987</v>
+        <v>4576</v>
       </c>
       <c r="R51" s="11">
-        <v>8820</v>
+        <v>6977</v>
       </c>
       <c r="S51" s="11">
-        <v>12523</v>
+        <v>12270</v>
       </c>
       <c r="T51" s="12">
         <f>SUM(L51:S51)</f>
-        <v>53742</v>
+        <v>63674</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="D52" s="9">
-        <v>37196</v>
+        <v>36840</v>
       </c>
       <c r="E52" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D52)/365.25,0)</f>
-        <v>23</v>
-      </c>
-      <c r="F52" s="10"/>
+        <v>24</v>
+      </c>
       <c r="G52" s="5" t="s">
         <v>2</v>
       </c>
@@ -6773,247 +6769,243 @@
         <v>3</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>11</v>
+        <v>219</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L52" s="11">
-        <v>7248</v>
+        <v>14072</v>
       </c>
       <c r="M52" s="11">
-        <v>3275</v>
+        <v>14620</v>
       </c>
       <c r="N52" s="11">
-        <v>11781</v>
+        <v>4735</v>
       </c>
       <c r="O52" s="11">
-        <v>12629</v>
+        <v>8710</v>
       </c>
       <c r="P52" s="11">
-        <v>10785</v>
+        <v>4442</v>
       </c>
       <c r="Q52" s="11">
-        <v>5707</v>
+        <v>14601</v>
       </c>
       <c r="R52" s="11">
-        <v>5363</v>
+        <v>13322</v>
       </c>
       <c r="S52" s="11">
-        <v>6897</v>
+        <v>3703</v>
       </c>
       <c r="T52" s="12">
         <f>SUM(L52:S52)</f>
-        <v>63685</v>
+        <v>78205</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="D53" s="9">
-        <v>37232</v>
+        <v>36958</v>
       </c>
       <c r="E53" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D53)/365.25,0)</f>
-        <v>23</v>
-      </c>
-      <c r="F53" s="10"/>
+        <v>24</v>
+      </c>
       <c r="G53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H53" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="J53" s="9" t="s">
         <v>11</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L53" s="11">
-        <v>10873</v>
+        <v>7751</v>
       </c>
       <c r="M53" s="11">
-        <v>11280</v>
+        <v>4810</v>
       </c>
       <c r="N53" s="11">
-        <v>11824</v>
+        <v>6694</v>
       </c>
       <c r="O53" s="11">
-        <v>1538</v>
+        <v>8552</v>
       </c>
       <c r="P53" s="11">
-        <v>2376</v>
+        <v>14526</v>
       </c>
       <c r="Q53" s="11">
-        <v>9456</v>
+        <v>6687</v>
       </c>
       <c r="R53" s="11">
-        <v>7948</v>
+        <v>12321</v>
       </c>
       <c r="S53" s="11">
-        <v>14935</v>
+        <v>9920</v>
       </c>
       <c r="T53" s="12">
         <f>SUM(L53:S53)</f>
-        <v>70230</v>
+        <v>71261</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="D54" s="9">
-        <v>37348</v>
+        <v>37159</v>
       </c>
       <c r="E54" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D54)/365.25,0)</f>
         <v>23</v>
       </c>
-      <c r="F54" s="10"/>
       <c r="G54" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L54" s="11">
-        <v>12244</v>
+        <v>9902</v>
       </c>
       <c r="M54" s="11">
-        <v>5924</v>
+        <v>13690</v>
       </c>
       <c r="N54" s="11">
-        <v>11878</v>
+        <v>7185</v>
       </c>
       <c r="O54" s="11">
-        <v>6507</v>
+        <v>11873</v>
       </c>
       <c r="P54" s="11">
-        <v>14299</v>
+        <v>10257</v>
       </c>
       <c r="Q54" s="11">
-        <v>5336</v>
+        <v>1153</v>
       </c>
       <c r="R54" s="11">
-        <v>10340</v>
+        <v>14091</v>
       </c>
       <c r="S54" s="11">
-        <v>1306</v>
+        <v>7430</v>
       </c>
       <c r="T54" s="12">
         <f>SUM(L54:S54)</f>
-        <v>67834</v>
+        <v>75581</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="D55" s="9">
-        <v>37357</v>
+        <v>37195</v>
       </c>
       <c r="E55" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D55)/365.25,0)</f>
         <v>23</v>
       </c>
-      <c r="F55" s="10"/>
       <c r="G55" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K55" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L55" s="11">
-        <v>13086</v>
+        <v>13971</v>
       </c>
       <c r="M55" s="11">
-        <v>5443</v>
+        <v>1233</v>
       </c>
       <c r="N55" s="11">
-        <v>6273</v>
+        <v>2339</v>
       </c>
       <c r="O55" s="11">
-        <v>9954</v>
+        <v>2920</v>
       </c>
       <c r="P55" s="11">
-        <v>10103</v>
+        <v>2949</v>
       </c>
       <c r="Q55" s="11">
-        <v>11905</v>
+        <v>8987</v>
       </c>
       <c r="R55" s="11">
-        <v>12906</v>
+        <v>8820</v>
       </c>
       <c r="S55" s="11">
-        <v>6207</v>
+        <v>12523</v>
       </c>
       <c r="T55" s="12">
         <f>SUM(L55:S55)</f>
-        <v>75877</v>
+        <v>53742</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="D56" s="9">
-        <v>37366</v>
+        <v>37478</v>
       </c>
       <c r="E56" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D56)/365.25,0)</f>
         <v>23</v>
       </c>
-      <c r="F56" s="10"/>
       <c r="G56" s="5" t="s">
         <v>2</v>
       </c>
@@ -7021,55 +7013,55 @@
         <v>2</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>8</v>
+        <v>220</v>
       </c>
       <c r="K56" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L56" s="11">
-        <v>7388</v>
+        <v>6402</v>
       </c>
       <c r="M56" s="11">
-        <v>13252</v>
+        <v>4411</v>
       </c>
       <c r="N56" s="11">
-        <v>8086</v>
+        <v>8397</v>
       </c>
       <c r="O56" s="11">
-        <v>12449</v>
+        <v>14587</v>
       </c>
       <c r="P56" s="11">
-        <v>6773</v>
+        <v>2417</v>
       </c>
       <c r="Q56" s="11">
-        <v>6821</v>
+        <v>3485</v>
       </c>
       <c r="R56" s="11">
-        <v>8276</v>
+        <v>4811</v>
       </c>
       <c r="S56" s="11">
-        <v>7906</v>
+        <v>13002</v>
       </c>
       <c r="T56" s="12">
         <f>SUM(L56:S56)</f>
-        <v>70951</v>
+        <v>57512</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D57" s="9">
-        <v>37478</v>
+        <v>37607</v>
       </c>
       <c r="E57" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D57)/365.25,0)</f>
@@ -7079,351 +7071,349 @@
         <v>2</v>
       </c>
       <c r="H57" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>220</v>
+        <v>11</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L57" s="11">
-        <v>6402</v>
+        <v>3072</v>
       </c>
       <c r="M57" s="11">
-        <v>4411</v>
+        <v>13683</v>
       </c>
       <c r="N57" s="11">
-        <v>8397</v>
+        <v>8161</v>
       </c>
       <c r="O57" s="11">
-        <v>14587</v>
+        <v>3528</v>
       </c>
       <c r="P57" s="11">
-        <v>2417</v>
+        <v>1030</v>
       </c>
       <c r="Q57" s="11">
-        <v>3485</v>
+        <v>10381</v>
       </c>
       <c r="R57" s="11">
-        <v>4811</v>
+        <v>7548</v>
       </c>
       <c r="S57" s="11">
-        <v>13002</v>
+        <v>4854</v>
       </c>
       <c r="T57" s="12">
         <f>SUM(L57:S57)</f>
-        <v>57512</v>
+        <v>52257</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="D58" s="9">
-        <v>37517</v>
+        <v>37644</v>
       </c>
       <c r="E58" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D58)/365.25,0)</f>
         <v>22</v>
       </c>
-      <c r="F58" s="10"/>
       <c r="G58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H58" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>11</v>
+        <v>219</v>
       </c>
       <c r="K58" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L58" s="11">
-        <v>10349</v>
+        <v>9307</v>
       </c>
       <c r="M58" s="11">
-        <v>14002</v>
+        <v>6303</v>
       </c>
       <c r="N58" s="11">
-        <v>6490</v>
+        <v>3968</v>
       </c>
       <c r="O58" s="11">
-        <v>11615</v>
+        <v>6785</v>
       </c>
       <c r="P58" s="11">
-        <v>12493</v>
+        <v>8801</v>
       </c>
       <c r="Q58" s="11">
-        <v>7547</v>
+        <v>6266</v>
       </c>
       <c r="R58" s="11">
-        <v>7388</v>
+        <v>13686</v>
       </c>
       <c r="S58" s="11">
-        <v>5190</v>
+        <v>4459</v>
       </c>
       <c r="T58" s="12">
         <f>SUM(L58:S58)</f>
-        <v>75074</v>
+        <v>59575</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D59" s="9">
-        <v>37607</v>
+        <v>37029</v>
       </c>
       <c r="E59" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D59)/365.25,0)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H59" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J59" s="9" t="s">
         <v>11</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L59" s="11">
-        <v>3072</v>
+        <v>14656</v>
       </c>
       <c r="M59" s="11">
-        <v>13683</v>
+        <v>10828</v>
       </c>
       <c r="N59" s="11">
-        <v>8161</v>
+        <v>7927</v>
       </c>
       <c r="O59" s="11">
-        <v>3528</v>
+        <v>8647</v>
       </c>
       <c r="P59" s="11">
-        <v>1030</v>
+        <v>10760</v>
       </c>
       <c r="Q59" s="11">
-        <v>10381</v>
+        <v>2441</v>
       </c>
       <c r="R59" s="11">
-        <v>7548</v>
+        <v>7360</v>
       </c>
       <c r="S59" s="11">
-        <v>4854</v>
+        <v>9385</v>
       </c>
       <c r="T59" s="12">
         <f>SUM(L59:S59)</f>
-        <v>52257</v>
+        <v>72004</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D60" s="9">
-        <v>37644</v>
+        <v>39180</v>
       </c>
       <c r="E60" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D60)/365.25,0)</f>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>219</v>
+        <v>13</v>
       </c>
       <c r="K60" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L60" s="11">
-        <v>9307</v>
+        <v>9823</v>
       </c>
       <c r="M60" s="11">
-        <v>6303</v>
+        <v>3238</v>
       </c>
       <c r="N60" s="11">
-        <v>3968</v>
+        <v>8111</v>
       </c>
       <c r="O60" s="11">
-        <v>6785</v>
+        <v>2537</v>
       </c>
       <c r="P60" s="11">
-        <v>8801</v>
+        <v>12217</v>
       </c>
       <c r="Q60" s="11">
-        <v>6266</v>
+        <v>1306</v>
       </c>
       <c r="R60" s="11">
-        <v>13686</v>
+        <v>11759</v>
       </c>
       <c r="S60" s="11">
-        <v>4459</v>
+        <v>8920</v>
       </c>
       <c r="T60" s="12">
         <f>SUM(L60:S60)</f>
-        <v>59575</v>
+        <v>57911</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D61" s="9">
-        <v>38005</v>
+        <v>36745</v>
       </c>
       <c r="E61" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D61)/365.25,0)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H61" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K61" s="5" t="s">
         <v>15</v>
       </c>
       <c r="L61" s="11">
-        <v>11765</v>
+        <v>10532</v>
       </c>
       <c r="M61" s="11">
-        <v>9493</v>
+        <v>14287</v>
       </c>
       <c r="N61" s="11">
-        <v>4483</v>
+        <v>1712</v>
       </c>
       <c r="O61" s="11">
-        <v>11577</v>
+        <v>4789</v>
       </c>
       <c r="P61" s="11">
-        <v>4989</v>
+        <v>2709</v>
       </c>
       <c r="Q61" s="11">
-        <v>6670</v>
+        <v>2977</v>
       </c>
       <c r="R61" s="11">
-        <v>4199</v>
+        <v>8390</v>
       </c>
       <c r="S61" s="11">
-        <v>7638</v>
+        <v>1113</v>
       </c>
       <c r="T61" s="12">
         <f>SUM(L61:S61)</f>
-        <v>60814</v>
+        <v>46509</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>158</v>
+        <v>218</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>279</v>
+        <v>156</v>
       </c>
       <c r="D62" s="9">
-        <v>38047</v>
+        <v>35773</v>
       </c>
       <c r="E62" s="5">
         <f ca="1">ROUNDDOWN((TODAY()-D62)/365.25,0)</f>
-        <v>21</v>
-      </c>
-      <c r="F62" s="10"/>
+        <v>27</v>
+      </c>
       <c r="G62" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>5</v>
+        <v>220</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L62" s="11">
-        <v>14767</v>
+        <v>10420</v>
       </c>
       <c r="M62" s="11">
-        <v>8994</v>
+        <v>13706</v>
       </c>
       <c r="N62" s="11">
-        <v>3061</v>
+        <v>8976</v>
       </c>
       <c r="O62" s="11">
-        <v>10262</v>
+        <v>5180</v>
       </c>
       <c r="P62" s="11">
-        <v>10822</v>
+        <v>12590</v>
       </c>
       <c r="Q62" s="11">
-        <v>1678</v>
+        <v>6698</v>
       </c>
       <c r="R62" s="11">
-        <v>8196</v>
+        <v>3975</v>
       </c>
       <c r="S62" s="11">
-        <v>13935</v>
+        <v>12042</v>
       </c>
       <c r="T62" s="12">
         <f>SUM(L62:S62)</f>
-        <v>71715</v>
+        <v>73587</v>
       </c>
     </row>
     <row r="66" spans="11:20" x14ac:dyDescent="0.25">
@@ -7492,7 +7482,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T62">
-    <sortCondition ref="D2:D62"/>
+    <sortCondition ref="A3:A62"/>
   </sortState>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V3:W3" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -7508,37 +7498,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Statusofmaterial xmlns="eac83ec6-6f47-45c8-8182-335b1d52a78e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="275339dd-7a42-4708-9a3d-cb97ad4c617e" xsi:nil="true"/>
-    <Comments xmlns="eac83ec6-6f47-45c8-8182-335b1d52a78e" xsi:nil="true"/>
-    <Comment xmlns="eac83ec6-6f47-45c8-8182-335b1d52a78e" xsi:nil="true"/>
-    <Software xmlns="eac83ec6-6f47-45c8-8182-335b1d52a78e" xsi:nil="true"/>
-    <Author_x002f_Owner xmlns="eac83ec6-6f47-45c8-8182-335b1d52a78e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Author_x002f_Owner>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eac83ec6-6f47-45c8-8182-335b1d52a78e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6275CE17C4B3743AA83EC4533F09972" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3eb2eb60ea590786764c08d8a72870ee">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eac83ec6-6f47-45c8-8182-335b1d52a78e" xmlns:ns3="275339dd-7a42-4708-9a3d-cb97ad4c617e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e743be182bdbd35c41bb49800bc014bd" ns2:_="" ns3:_="">
     <xsd:import namespace="eac83ec6-6f47-45c8-8182-335b1d52a78e"/>
@@ -7886,26 +7845,38 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACA82DD5-2559-451B-96DB-E39B625FB399}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eac83ec6-6f47-45c8-8182-335b1d52a78e"/>
-    <ds:schemaRef ds:uri="275339dd-7a42-4708-9a3d-cb97ad4c617e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9A85F60-0980-4F8E-AB71-83E6ED8E6EB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Statusofmaterial xmlns="eac83ec6-6f47-45c8-8182-335b1d52a78e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="275339dd-7a42-4708-9a3d-cb97ad4c617e" xsi:nil="true"/>
+    <Comments xmlns="eac83ec6-6f47-45c8-8182-335b1d52a78e" xsi:nil="true"/>
+    <Comment xmlns="eac83ec6-6f47-45c8-8182-335b1d52a78e" xsi:nil="true"/>
+    <Software xmlns="eac83ec6-6f47-45c8-8182-335b1d52a78e" xsi:nil="true"/>
+    <Author_x002f_Owner xmlns="eac83ec6-6f47-45c8-8182-335b1d52a78e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Author_x002f_Owner>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eac83ec6-6f47-45c8-8182-335b1d52a78e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B424E03A-6243-4350-84BC-B5F3AD273463}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7922,4 +7893,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9A85F60-0980-4F8E-AB71-83E6ED8E6EB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACA82DD5-2559-451B-96DB-E39B625FB399}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eac83ec6-6f47-45c8-8182-335b1d52a78e"/>
+    <ds:schemaRef ds:uri="275339dd-7a42-4708-9a3d-cb97ad4c617e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>